--- a/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/PivotCacheWithoutSourceData-output.xlsx
+++ b/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/PivotCacheWithoutSourceData-output.xlsx
@@ -235,7 +235,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:pivotCacheDefinition xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" saveData="0" refreshOnLoad="1" refreshedBy="Jan Havlíček" refreshedDate="45202.937231134259" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="3" xr:uid="{4B218844-6C63-4A82-95E2-9FCF588AAF15}" mc:Ignorable="xr">
+<x:pivotCacheDefinition xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" saveData="0" refreshOnLoad="0" refreshedBy="Jan Havlíček" refreshedDate="45202.937231134259" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="3" xr:uid="{4B218844-6C63-4A82-95E2-9FCF588AAF15}" mc:Ignorable="xr">
   <x:cacheSource type="worksheet">
     <x:worksheetSource ref="A1:B4" sheet="Sheet1"/>
   </x:cacheSource>

--- a/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/PivotCacheWithoutSourceData-output.xlsx
+++ b/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/PivotCacheWithoutSourceData-output.xlsx
@@ -200,8 +200,35 @@
       <x:diagonal/>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="2">
+  <x:cellStyleXfs count="11">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="14" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -580,7 +607,98 @@
   <x:cols>
     <x:col min="1" max="2" width="15.855469" style="0" bestFit="1" customWidth="1"/>
   </x:cols>
-  <x:sheetData/>
+  <x:sheetData>
+    <x:row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <x:c r="A3" s="2"/>
+      <x:c r="B3" s="3"/>
+      <x:c r="C3" s="4"/>
+    </x:row>
+    <x:row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <x:c r="A4" s="5"/>
+      <x:c r="B4" s="6"/>
+      <x:c r="C4" s="7"/>
+    </x:row>
+    <x:row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <x:c r="A5" s="5"/>
+      <x:c r="B5" s="6"/>
+      <x:c r="C5" s="7"/>
+    </x:row>
+    <x:row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <x:c r="A6" s="5"/>
+      <x:c r="B6" s="6"/>
+      <x:c r="C6" s="7"/>
+    </x:row>
+    <x:row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <x:c r="A7" s="5"/>
+      <x:c r="B7" s="6"/>
+      <x:c r="C7" s="7"/>
+    </x:row>
+    <x:row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <x:c r="A8" s="5"/>
+      <x:c r="B8" s="6"/>
+      <x:c r="C8" s="7"/>
+    </x:row>
+    <x:row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <x:c r="A9" s="5"/>
+      <x:c r="B9" s="6"/>
+      <x:c r="C9" s="7"/>
+    </x:row>
+    <x:row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <x:c r="A10" s="5"/>
+      <x:c r="B10" s="6"/>
+      <x:c r="C10" s="7"/>
+    </x:row>
+    <x:row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <x:c r="A11" s="5"/>
+      <x:c r="B11" s="6"/>
+      <x:c r="C11" s="7"/>
+    </x:row>
+    <x:row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <x:c r="A12" s="5"/>
+      <x:c r="B12" s="6"/>
+      <x:c r="C12" s="7"/>
+    </x:row>
+    <x:row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <x:c r="A13" s="5"/>
+      <x:c r="B13" s="6"/>
+      <x:c r="C13" s="7"/>
+    </x:row>
+    <x:row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <x:c r="A14" s="5"/>
+      <x:c r="B14" s="6"/>
+      <x:c r="C14" s="7"/>
+    </x:row>
+    <x:row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <x:c r="A15" s="5"/>
+      <x:c r="B15" s="6"/>
+      <x:c r="C15" s="7"/>
+    </x:row>
+    <x:row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <x:c r="A16" s="5"/>
+      <x:c r="B16" s="6"/>
+      <x:c r="C16" s="7"/>
+    </x:row>
+    <x:row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <x:c r="A17" s="5"/>
+      <x:c r="B17" s="6"/>
+      <x:c r="C17" s="7"/>
+    </x:row>
+    <x:row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <x:c r="A18" s="5"/>
+      <x:c r="B18" s="6"/>
+      <x:c r="C18" s="7"/>
+    </x:row>
+    <x:row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <x:c r="A19" s="5"/>
+      <x:c r="B19" s="6"/>
+      <x:c r="C19" s="7"/>
+    </x:row>
+    <x:row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <x:c r="A20" s="8"/>
+      <x:c r="B20" s="9"/>
+      <x:c r="C20" s="10"/>
+    </x:row>
+  </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>

--- a/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/PivotCacheWithoutSourceData-output.xlsx
+++ b/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/PivotCacheWithoutSourceData-output.xlsx
@@ -293,7 +293,7 @@
     <pivotField showAll="0"/>
     <pivotField numFmtId="14" showAll="0"/>
   </pivotFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1"/>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
       <x14:pivotTableDefinition enableEdit="0" hideValuesRow="1"/>
